--- a/artfynd/S 4775-2024 artfynd.xlsx
+++ b/artfynd/S 4775-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476423</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476424</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476426</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476427</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476430</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1797,6 +1842,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476431</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1922,6 +1972,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476432</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2047,6 +2102,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476433</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2297,6 +2362,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/476435</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2425,6 +2495,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932558</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2553,6 +2628,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932559</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2681,6 +2761,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932560</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2809,6 +2894,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932561</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2937,6 +3027,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932562</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3065,6 +3160,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932563</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3193,6 +3293,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3321,6 +3426,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3449,6 +3559,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932566</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3577,6 +3692,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932567</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3705,6 +3825,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932568</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3833,6 +3958,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932569</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3961,6 +4091,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76932570</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4078,6 +4213,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108586581</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4215,6 +4355,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4347,6 +4492,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587705</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4479,6 +4629,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587935</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4596,6 +4751,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588156</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4713,6 +4873,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588657</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4830,6 +4995,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705192</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4949,6 +5119,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705584</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5058,6 +5233,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705723</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5175,6 +5355,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108705841</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5284,6 +5469,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116035595</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5393,6 +5583,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116036546</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5502,6 +5697,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037802</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5611,6 +5811,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037843</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5720,6 +5925,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116037988</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5829,6 +6039,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116038032</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5931,6 +6146,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158228</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6033,6 +6253,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158229</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6135,6 +6360,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158230</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6237,6 +6467,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158231</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6339,6 +6574,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158232</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6459,6 +6699,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805706</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6579,6 +6824,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805707</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6699,6 +6949,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805708</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6819,6 +7074,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805709</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6939,6 +7199,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805711</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7059,6 +7324,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805713</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7179,6 +7449,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805715</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7299,6 +7574,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805716</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7419,6 +7699,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805717</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7539,6 +7824,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805718</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7659,6 +7949,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805719</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7779,6 +8074,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805720</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7899,6 +8199,11 @@
           <t>Åtgärdsprogram för rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122805721</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8029,6 +8334,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893390</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8159,6 +8469,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893391</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8289,6 +8604,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893392</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8419,6 +8739,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893393</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8549,6 +8874,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893394</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8679,6 +9009,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893395</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8809,6 +9144,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893396</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8939,6 +9279,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893398</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9069,6 +9414,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893399</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9199,6 +9549,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893400</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9329,6 +9684,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893401</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9459,6 +9819,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893402</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9589,6 +9954,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893403</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9719,6 +10089,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893404</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9849,6 +10224,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893405</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9979,6 +10359,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893406</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10109,6 +10494,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131893407</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10206,6 +10596,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158226</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10303,6 +10698,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158235</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10419,6 +10819,11 @@
           <t>Åtgärdsprogram rökpipsvamp</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1170590</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10516,6 +10921,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158234</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10618,6 +11028,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2204521</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10739,6 +11154,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587921</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10856,6 +11276,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108588735</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10953,6 +11378,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158221</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11050,6 +11480,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158222</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11147,6 +11582,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158223</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11244,6 +11684,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158224</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11341,6 +11786,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158225</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11447,6 +11897,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62421602</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11549,6 +12004,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2632921</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11660,6 +12120,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62155610</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11766,6 +12231,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59870549</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11872,6 +12342,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59870550</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11974,6 +12449,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62124149</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12071,6 +12551,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62057620</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12178,6 +12663,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62057621</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12280,6 +12770,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531177</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12387,6 +12882,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531179</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12489,6 +12989,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5019490</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12591,6 +13096,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082620</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12688,6 +13198,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161229</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12785,6 +13300,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161230</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12887,6 +13407,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59855075</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12989,6 +13514,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59855076</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13091,8 +13621,121 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62505214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>